--- a/output/graficos_dimensiones/comunal_d_env_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:16</t>
+    <t xml:space="preserve">2026-09-10 01:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:30</t>
+    <t xml:space="preserve">2026-09-12 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_biobio.xlsx
@@ -42,27 +42,27 @@
     <t xml:space="preserve">Yumbel</t>
   </si>
   <si>
+    <t xml:space="preserve">San Rosendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilleco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Florida</t>
   </si>
   <si>
-    <t xml:space="preserve">Quilleco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rosendo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Concepción</t>
   </si>
   <si>
+    <t xml:space="preserve">Antuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lota</t>
   </si>
   <si>
     <t xml:space="preserve">Tomé</t>
   </si>
   <si>
-    <t xml:space="preserve">Antuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
@@ -96,12 +96,12 @@
     <t xml:space="preserve">Santa Juana</t>
   </si>
   <si>
+    <t xml:space="preserve">Negrete</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nacimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Negrete</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cabrero</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:41</t>
+    <t xml:space="preserve">2026-09-24 00:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -577,7 +577,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>159.91</v>
+        <v>169.78</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>139.96</v>
+        <v>151.42</v>
       </c>
     </row>
     <row r="4">
@@ -605,13 +605,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8104</v>
+        <v>8310</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>136.88</v>
+        <v>150.43</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>136.36</v>
+        <v>146.85</v>
       </c>
     </row>
     <row r="6">
@@ -639,13 +639,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8310</v>
+        <v>8104</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>135.13</v>
+        <v>145.81</v>
       </c>
     </row>
     <row r="7">
@@ -662,7 +662,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>133.41</v>
+        <v>143.4</v>
       </c>
     </row>
     <row r="8">
@@ -673,13 +673,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>8106</v>
+        <v>8302</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>127.9</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
@@ -690,13 +690,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>8111</v>
+        <v>8106</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>127.66</v>
+        <v>138.41</v>
       </c>
     </row>
     <row r="10">
@@ -707,13 +707,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>8302</v>
+        <v>8111</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>127.62</v>
+        <v>137.92</v>
       </c>
     </row>
     <row r="11">
@@ -730,7 +730,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>124.57</v>
+        <v>134.13</v>
       </c>
     </row>
     <row r="12">
@@ -747,7 +747,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>122.09</v>
+        <v>131.97</v>
       </c>
     </row>
     <row r="13">
@@ -764,7 +764,7 @@
         <v>2020</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>115.71</v>
+        <v>124.33</v>
       </c>
     </row>
     <row r="14">
@@ -781,7 +781,7 @@
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>114.42</v>
+        <v>123.73</v>
       </c>
     </row>
     <row r="15">
@@ -798,7 +798,7 @@
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>111.63</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="16">
@@ -815,7 +815,7 @@
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>110.33</v>
+        <v>119.42</v>
       </c>
     </row>
     <row r="17">
@@ -832,7 +832,7 @@
         <v>2020</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>109.35</v>
+        <v>118.54</v>
       </c>
     </row>
     <row r="18">
@@ -849,7 +849,7 @@
         <v>2020</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>109.2</v>
+        <v>117.07</v>
       </c>
     </row>
     <row r="19">
@@ -866,7 +866,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>107.4</v>
+        <v>116.7</v>
       </c>
     </row>
     <row r="20">
@@ -883,7 +883,7 @@
         <v>2020</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>106.86</v>
+        <v>115.45</v>
       </c>
     </row>
     <row r="21">
@@ -900,7 +900,7 @@
         <v>2020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>106.68</v>
+        <v>114.95</v>
       </c>
     </row>
     <row r="22">
@@ -911,13 +911,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>8306</v>
+        <v>8307</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>101.01</v>
+        <v>109.79</v>
       </c>
     </row>
     <row r="23">
@@ -928,13 +928,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>8307</v>
+        <v>8306</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>100.8</v>
+        <v>109.46</v>
       </c>
     </row>
     <row r="24">
@@ -951,7 +951,7 @@
         <v>2020</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>97.23</v>
+        <v>105.26</v>
       </c>
     </row>
     <row r="25">
@@ -968,7 +968,7 @@
         <v>2020</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>91.9</v>
+        <v>98.79</v>
       </c>
     </row>
     <row r="26">
@@ -985,7 +985,7 @@
         <v>2020</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>89.17</v>
+        <v>96.27</v>
       </c>
     </row>
     <row r="27">
@@ -1002,7 +1002,7 @@
         <v>2020</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>86.79</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="28">
@@ -1019,7 +1019,7 @@
         <v>2020</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>85.62</v>
+        <v>92.66</v>
       </c>
     </row>
     <row r="29">
@@ -1036,7 +1036,7 @@
         <v>2020</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>84.84</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="30">
@@ -1053,7 +1053,7 @@
         <v>2020</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>80.74</v>
+        <v>86.92</v>
       </c>
     </row>
     <row r="31">
@@ -1070,7 +1070,7 @@
         <v>2020</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>74.45</v>
+        <v>80.43</v>
       </c>
     </row>
     <row r="32">
@@ -1087,7 +1087,7 @@
         <v>2020</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>69.04</v>
+        <v>74.12</v>
       </c>
     </row>
     <row r="33">
@@ -1104,7 +1104,7 @@
         <v>2020</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>61.34</v>
+        <v>66.07</v>
       </c>
     </row>
     <row r="34">
@@ -1121,7 +1121,7 @@
         <v>2020</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>46.47</v>
+        <v>50.42</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:10</t>
+    <t xml:space="preserve">2026-10-02 16:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_biobio.xlsx
@@ -117,13 +117,13 @@
     <t xml:space="preserve">Hualqui</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Cañete</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:10</t>
+    <t xml:space="preserve">2026-10-04 10:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:40</t>
+    <t xml:space="preserve">2026-10-05 16:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
